--- a/tools/importer/reports/import-faqs.report.xlsx
+++ b/tools/importer/reports/import-faqs.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-09-02T06:21:16.767Z</t>
+    <t>2026-09-02T13:41:40.933Z</t>
   </si>
   <si>
     <t>WKND Adventures and Travel</t>
@@ -73,7 +73,7 @@
     <t>about-us</t>
   </si>
   <si>
-    <t>2026-09-01T18:04:39.878Z</t>
+    <t>2026-09-02T13:41:49.052Z</t>
   </si>
   <si>
     <t>About Us</t>
@@ -94,7 +94,7 @@
     <t>adventure-index</t>
   </si>
   <si>
-    <t>2026-09-02T05:46:12.970Z</t>
+    <t>2026-09-02T13:41:55.978Z</t>
   </si>
   <si>
     <t>Adventures</t>
@@ -115,7 +115,7 @@
     <t>faqs</t>
   </si>
   <si>
-    <t>2026-09-02T12:07:24.976Z</t>
+    <t>2026-09-02T13:42:10.074Z</t>
   </si>
   <si>
     <t>FAQs</t>
@@ -127,7 +127,7 @@
     <t>us/en/magazine.report.json</t>
   </si>
   <si>
-    <t>["columns","cards"]</t>
+    <t>["columns","columns","columns","cards"]</t>
   </si>
   <si>
     <t>us/en/magazine</t>
@@ -136,7 +136,7 @@
     <t>magazine</t>
   </si>
   <si>
-    <t>2026-09-02T03:05:01.851Z</t>
+    <t>2026-09-02T13:42:02.961Z</t>
   </si>
   <si>
     <t>Magazine</t>
@@ -157,7 +157,7 @@
     <t>adventure-detail</t>
   </si>
   <si>
-    <t>2026-09-02T03:49:29.531Z</t>
+    <t>2026-09-02T12:47:29.254Z</t>
   </si>
   <si>
     <t>Bali Surf Camp</t>
@@ -172,7 +172,7 @@
     <t>us/en/adventures/beervana-portland</t>
   </si>
   <si>
-    <t>2026-09-02T03:49:34.803Z</t>
+    <t>2026-09-02T12:47:34.792Z</t>
   </si>
   <si>
     <t>Beervana in Portland</t>
@@ -187,7 +187,7 @@
     <t>us/en/adventures/climbing-new-zealand</t>
   </si>
   <si>
-    <t>2026-09-02T03:49:40.773Z</t>
+    <t>2026-09-02T12:47:39.310Z</t>
   </si>
   <si>
     <t>Climbing New Zealand</t>
@@ -202,7 +202,7 @@
     <t>us/en/adventures/colorado-rock-climbing</t>
   </si>
   <si>
-    <t>2026-09-02T03:49:45.297Z</t>
+    <t>2026-09-02T12:47:44.996Z</t>
   </si>
   <si>
     <t>Colorado Rock Climbing</t>
@@ -217,7 +217,7 @@
     <t>us/en/adventures/cycling-southern-utah</t>
   </si>
   <si>
-    <t>2026-09-02T03:49:51.071Z</t>
+    <t>2026-09-02T12:47:50.992Z</t>
   </si>
   <si>
     <t>Cycling Southern Utah</t>
@@ -232,7 +232,7 @@
     <t>us/en/adventures/cycling-tuscany</t>
   </si>
   <si>
-    <t>2026-09-02T03:49:56.493Z</t>
+    <t>2026-09-02T12:47:55.576Z</t>
   </si>
   <si>
     <t>Cycling Tuscany</t>
@@ -247,7 +247,7 @@
     <t>us/en/adventures/downhill-skiing-wyoming</t>
   </si>
   <si>
-    <t>2026-09-02T03:50:03.034Z</t>
+    <t>2026-09-02T12:48:00.458Z</t>
   </si>
   <si>
     <t>Downhill Skiing Wyoming</t>
@@ -262,7 +262,7 @@
     <t>us/en/adventures/gastronomic-marais-tour</t>
   </si>
   <si>
-    <t>2026-09-02T03:50:09.889Z</t>
+    <t>2026-09-02T12:48:05.322Z</t>
   </si>
   <si>
     <t>Gastronomic Marais Tour</t>
@@ -277,7 +277,7 @@
     <t>us/en/adventures/napa-wine-tasting</t>
   </si>
   <si>
-    <t>2026-09-02T03:50:15.454Z</t>
+    <t>2026-09-02T12:48:09.491Z</t>
   </si>
   <si>
     <t>Napa Wine Tasting</t>
@@ -292,7 +292,7 @@
     <t>us/en/adventures/riverside-camping-australia</t>
   </si>
   <si>
-    <t>2026-09-02T03:50:21.671Z</t>
+    <t>2026-09-02T12:48:14.608Z</t>
   </si>
   <si>
     <t>Riverside Camping</t>
@@ -307,7 +307,7 @@
     <t>us/en/adventures/ski-touring-mont-blanc</t>
   </si>
   <si>
-    <t>2026-09-02T03:50:28.487Z</t>
+    <t>2026-09-02T12:48:18.666Z</t>
   </si>
   <si>
     <t>Ski Touring Mont Blanc</t>
@@ -322,7 +322,7 @@
     <t>us/en/adventures/surf-camp-costa-rica</t>
   </si>
   <si>
-    <t>2026-09-02T03:50:33.771Z</t>
+    <t>2026-09-02T12:48:23.811Z</t>
   </si>
   <si>
     <t>Surf Camp in Costa Rica</t>
@@ -337,7 +337,7 @@
     <t>us/en/adventures/tahoe-skiing</t>
   </si>
   <si>
-    <t>2026-09-02T03:50:38.682Z</t>
+    <t>2026-09-02T12:48:28.940Z</t>
   </si>
   <si>
     <t>Tahoe Skiing</t>
@@ -352,7 +352,7 @@
     <t>us/en/adventures/west-coast-cycling</t>
   </si>
   <si>
-    <t>2026-09-02T03:50:44.269Z</t>
+    <t>2026-09-02T12:48:34.067Z</t>
   </si>
   <si>
     <t>West Coast Cycling</t>
@@ -367,7 +367,7 @@
     <t>us/en/adventures/whistler-mountain-biking</t>
   </si>
   <si>
-    <t>2026-09-02T03:50:49.016Z</t>
+    <t>2026-09-02T12:48:39.260Z</t>
   </si>
   <si>
     <t>Whistler Mountain Biking</t>
@@ -382,7 +382,7 @@
     <t>us/en/adventures/yosemite-backpacking</t>
   </si>
   <si>
-    <t>2026-09-02T03:50:54.458Z</t>
+    <t>2026-09-02T12:48:44.505Z</t>
   </si>
   <si>
     <t>Yosemite Backpacking</t>
@@ -403,7 +403,7 @@
     <t>magazine-article</t>
   </si>
   <si>
-    <t>2026-09-02T11:44:41.970Z</t>
+    <t>2026-09-02T12:40:23.016Z</t>
   </si>
   <si>
     <t>Arctic Surfing</t>
@@ -418,7 +418,7 @@
     <t>us/en/magazine/guide-la-skateparks</t>
   </si>
   <si>
-    <t>2026-09-02T11:44:48.713Z</t>
+    <t>2026-09-02T12:40:27.258Z</t>
   </si>
   <si>
     <t>Ultimate Guide to LA Skateparks</t>
@@ -433,7 +433,7 @@
     <t>us/en/magazine/san-diego-surf</t>
   </si>
   <si>
-    <t>2026-09-02T11:44:53.926Z</t>
+    <t>2026-09-02T12:40:31.284Z</t>
   </si>
   <si>
     <t>San Diego Surf Spots</t>
@@ -448,7 +448,7 @@
     <t>us/en/magazine/ski-touring</t>
   </si>
   <si>
-    <t>2026-09-02T11:44:59.616Z</t>
+    <t>2026-09-02T12:40:37.418Z</t>
   </si>
   <si>
     <t>Ski Touring</t>
@@ -463,7 +463,7 @@
     <t>us/en/magazine/western-australia</t>
   </si>
   <si>
-    <t>2026-09-02T11:45:05.293Z</t>
+    <t>2026-09-02T12:40:41.847Z</t>
   </si>
   <si>
     <t>Western Australia</t>
